--- a/00 - Tests/03 - MID/03 - Delete/01 - Demand/Data.xlsx
+++ b/00 - Tests/03 - MID/03 - Delete/01 - Demand/Data.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mao8ct\Desktop\PyAutomateSAP\04 - MID\03 - Delete\01 - Demand\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mao8ct\Desktop\PyAutomateSAP\00 - Tests\03 - MID\03 - Delete\01 - Demand\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E81B04-6481-4DEC-A7D1-329A89D033C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37CE5DB4-6B38-4ED8-B883-B311DB1DFC99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{841C4129-0CB3-4066-B34E-E8845E3509BE}"/>
   </bookViews>
   <sheets>
     <sheet name="LocInst" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LocInst!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">LocInst!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -114,7 +114,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,279 +428,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D997F1F-30FE-4A2A-B694-A9178A4FC344}">
-  <dimension ref="A1:M46"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>685601397299</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601471797</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>685601397301</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601471795</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>685601402487</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601471377</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>685601406960</v>
-      </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601471136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>685601410319</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601468979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>685601410318</v>
-      </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601468940</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>685601410314</v>
-      </c>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601459170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>685601410312</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601459022</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>685601409761</v>
-      </c>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601458996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>685601409760</v>
-      </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601458992</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>685601409574</v>
-      </c>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601456871</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>685601409573</v>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601456870</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>685601409571</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601456869</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>685601409109</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>685601456868</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>685601409108</v>
+        <v>685601456867</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>685601409107</v>
+        <v>685601456866</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>685601408944</v>
+        <v>685601456865</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>685601408091</v>
+        <v>685601456864</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>685601407528</v>
+        <v>685601456863</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2">
-        <v>685601413739</v>
-      </c>
+      <c r="A21" s="2"/>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2">
-        <v>685601413111</v>
-      </c>
+      <c r="A22" s="2"/>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2">
-        <v>685601413110</v>
-      </c>
+      <c r="A23" s="2"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2">
-        <v>685601413109</v>
-      </c>
+      <c r="A24" s="2"/>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2">
-        <v>685601413108</v>
-      </c>
+      <c r="A25" s="2"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2">
-        <v>685601413107</v>
-      </c>
+      <c r="A26" s="2"/>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2">
-        <v>685601413105</v>
-      </c>
+      <c r="A27" s="2"/>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2">
-        <v>685601413103</v>
-      </c>
+      <c r="A28" s="2"/>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2">
-        <v>685601413067</v>
-      </c>
+      <c r="A29" s="2"/>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2">
-        <v>685601412900</v>
-      </c>
+      <c r="A30" s="2"/>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2">
-        <v>685601412899</v>
-      </c>
+      <c r="A31" s="2"/>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2">
-        <v>685601412777</v>
-      </c>
+      <c r="A32" s="2"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>685601411200</v>
-      </c>
+      <c r="A33" s="2"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2">
-        <v>685601410322</v>
-      </c>
+      <c r="A34" s="2"/>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>685601410320</v>
-      </c>
+      <c r="A35" s="2"/>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>685601418247</v>
-      </c>
+      <c r="A36" s="2"/>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>685601418125</v>
-      </c>
+      <c r="A37" s="2"/>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>685601417923</v>
-      </c>
+      <c r="A38" s="2"/>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>685601417922</v>
-      </c>
+      <c r="A39" s="2"/>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>685601416976</v>
-      </c>
+      <c r="A40" s="2"/>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>685601416975</v>
-      </c>
+      <c r="A41" s="2"/>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>685601416706</v>
-      </c>
+      <c r="A42" s="2"/>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>685601416704</v>
-      </c>
+      <c r="A43" s="2"/>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>685601416703</v>
-      </c>
+      <c r="A44" s="2"/>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2">
-        <v>685601414925</v>
-      </c>
+      <c r="A45" s="2"/>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2">
-        <v>685601414761</v>
-      </c>
+      <c r="A46" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
